--- a/research/traditional_assets/database/data/taiwan/taiwan_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/taiwan/taiwan_precious_metals.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0257</v>
+        <v>-0.0906</v>
       </c>
       <c r="G2">
-        <v>-0.03408917197452229</v>
+        <v>-0.02634146341463414</v>
       </c>
       <c r="H2">
-        <v>-0.0356687898089172</v>
+        <v>-0.02902439024390244</v>
       </c>
       <c r="I2">
-        <v>-0.03821656050955414</v>
+        <v>-0.08414634146341464</v>
       </c>
       <c r="J2">
-        <v>-0.03821656050955414</v>
+        <v>-0.08414634146341464</v>
       </c>
       <c r="K2">
-        <v>-3.72</v>
+        <v>-3.27</v>
       </c>
       <c r="L2">
-        <v>-0.04738853503184714</v>
+        <v>-0.07975609756097561</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2.71</v>
+        <v>4</v>
       </c>
       <c r="V2">
-        <v>0.04221183800623052</v>
+        <v>0.06015037593984962</v>
       </c>
       <c r="W2">
-        <v>-0.06631016042780749</v>
+        <v>-0.05978062157221206</v>
       </c>
       <c r="X2">
-        <v>0.08579130858259977</v>
+        <v>0.1524809111683281</v>
       </c>
       <c r="Y2">
-        <v>-0.1521014690104073</v>
+        <v>-0.2122615327405402</v>
       </c>
       <c r="Z2">
-        <v>0.8296343267808075</v>
+        <v>0.4244745832901956</v>
       </c>
       <c r="AA2">
-        <v>-0.03170577045022194</v>
+        <v>-0.03571798322807743</v>
       </c>
       <c r="AB2">
-        <v>0.05996593700924166</v>
+        <v>0.1138804962909984</v>
       </c>
       <c r="AC2">
-        <v>-0.0916717074594636</v>
+        <v>-0.1495984795190758</v>
       </c>
       <c r="AD2">
-        <v>44.6</v>
+        <v>40.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>44.6</v>
+        <v>40.1</v>
       </c>
       <c r="AG2">
-        <v>41.89</v>
+        <v>36.1</v>
       </c>
       <c r="AH2">
-        <v>0.4099264705882353</v>
+        <v>0.376172607879925</v>
       </c>
       <c r="AI2">
-        <v>0.4491440080563947</v>
+        <v>0.4723203769140165</v>
       </c>
       <c r="AJ2">
-        <v>0.3948534263361297</v>
+        <v>0.3518518518518519</v>
       </c>
       <c r="AK2">
-        <v>0.433688787659178</v>
+        <v>0.4462299134734239</v>
       </c>
       <c r="AL2">
-        <v>0.498</v>
+        <v>0.556</v>
       </c>
       <c r="AM2">
-        <v>0.452</v>
+        <v>0.504</v>
       </c>
       <c r="AN2">
-        <v>-39.82142857142857</v>
+        <v>-24.60122699386503</v>
       </c>
       <c r="AO2">
-        <v>-6.024096385542169</v>
+        <v>-6.205035971223022</v>
       </c>
       <c r="AP2">
-        <v>-37.40178571428571</v>
+        <v>-22.14723926380368</v>
       </c>
       <c r="AQ2">
-        <v>-6.63716814159292</v>
+        <v>-6.845238095238096</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0257</v>
+        <v>-0.0906</v>
       </c>
       <c r="G3">
-        <v>-0.03408917197452229</v>
+        <v>-0.02634146341463414</v>
       </c>
       <c r="H3">
-        <v>-0.0356687898089172</v>
+        <v>-0.02902439024390244</v>
       </c>
       <c r="I3">
-        <v>-0.03821656050955414</v>
+        <v>-0.08414634146341464</v>
       </c>
       <c r="J3">
-        <v>-0.03821656050955414</v>
+        <v>-0.08414634146341464</v>
       </c>
       <c r="K3">
-        <v>-3.72</v>
+        <v>-3.27</v>
       </c>
       <c r="L3">
-        <v>-0.04738853503184714</v>
+        <v>-0.07975609756097561</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.71</v>
+        <v>4</v>
       </c>
       <c r="V3">
-        <v>0.04221183800623052</v>
+        <v>0.06015037593984962</v>
       </c>
       <c r="W3">
-        <v>-0.06631016042780749</v>
+        <v>-0.05978062157221206</v>
       </c>
       <c r="X3">
-        <v>0.08579130858259977</v>
+        <v>0.1524809111683281</v>
       </c>
       <c r="Y3">
-        <v>-0.1521014690104073</v>
+        <v>-0.2122615327405402</v>
       </c>
       <c r="Z3">
-        <v>0.8296343267808075</v>
+        <v>0.4244745832901956</v>
       </c>
       <c r="AA3">
-        <v>-0.03170577045022194</v>
+        <v>-0.03571798322807743</v>
       </c>
       <c r="AB3">
-        <v>0.05996593700924166</v>
+        <v>0.1138804962909984</v>
       </c>
       <c r="AC3">
-        <v>-0.0916717074594636</v>
+        <v>-0.1495984795190758</v>
       </c>
       <c r="AD3">
-        <v>44.6</v>
+        <v>40.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>44.6</v>
+        <v>40.1</v>
       </c>
       <c r="AG3">
-        <v>41.89</v>
+        <v>36.1</v>
       </c>
       <c r="AH3">
-        <v>0.4099264705882353</v>
+        <v>0.376172607879925</v>
       </c>
       <c r="AI3">
-        <v>0.4491440080563947</v>
+        <v>0.4723203769140165</v>
       </c>
       <c r="AJ3">
-        <v>0.3948534263361297</v>
+        <v>0.3518518518518519</v>
       </c>
       <c r="AK3">
-        <v>0.433688787659178</v>
+        <v>0.4462299134734239</v>
       </c>
       <c r="AL3">
-        <v>0.498</v>
+        <v>0.556</v>
       </c>
       <c r="AM3">
-        <v>0.452</v>
+        <v>0.504</v>
       </c>
       <c r="AN3">
-        <v>-39.82142857142857</v>
+        <v>-24.60122699386503</v>
       </c>
       <c r="AO3">
-        <v>-6.024096385542169</v>
+        <v>-6.205035971223022</v>
       </c>
       <c r="AP3">
-        <v>-37.40178571428571</v>
+        <v>-22.14723926380368</v>
       </c>
       <c r="AQ3">
-        <v>-6.63716814159292</v>
+        <v>-6.845238095238096</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/taiwan/taiwan_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/taiwan/taiwan_precious_metals.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0906</v>
+        <v>-0.126</v>
       </c>
       <c r="G2">
-        <v>-0.02634146341463414</v>
+        <v>-0.0346264367816092</v>
       </c>
       <c r="H2">
-        <v>-0.02902439024390244</v>
+        <v>-0.03821839080459771</v>
       </c>
       <c r="I2">
-        <v>-0.08414634146341464</v>
+        <v>-0.06810344827586208</v>
       </c>
       <c r="J2">
-        <v>-0.08414634146341464</v>
+        <v>-0.06810344827586208</v>
       </c>
       <c r="K2">
-        <v>-3.27</v>
+        <v>-2.56</v>
       </c>
       <c r="L2">
-        <v>-0.07975609756097561</v>
+        <v>-0.07356321839080461</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="V2">
-        <v>0.06015037593984962</v>
+        <v>0.0291970802919708</v>
       </c>
       <c r="W2">
-        <v>-0.05978062157221206</v>
+        <v>-0.05714285714285715</v>
       </c>
       <c r="X2">
-        <v>0.1524809111683281</v>
+        <v>0.1196631312230006</v>
       </c>
       <c r="Y2">
-        <v>-0.2122615327405402</v>
+        <v>-0.1768059883658577</v>
       </c>
       <c r="Z2">
-        <v>0.4244745832901956</v>
+        <v>0.4301606922126081</v>
       </c>
       <c r="AA2">
-        <v>-0.03571798322807743</v>
+        <v>-0.02929542645241038</v>
       </c>
       <c r="AB2">
-        <v>0.1138804962909984</v>
+        <v>0.09402452015215366</v>
       </c>
       <c r="AC2">
-        <v>-0.1495984795190758</v>
+        <v>-0.1233199466045641</v>
       </c>
       <c r="AD2">
-        <v>40.1</v>
+        <v>43.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>40.1</v>
+        <v>43.8</v>
       </c>
       <c r="AG2">
-        <v>36.1</v>
+        <v>41.4</v>
       </c>
       <c r="AH2">
-        <v>0.376172607879925</v>
+        <v>0.3476190476190476</v>
       </c>
       <c r="AI2">
-        <v>0.4723203769140165</v>
+        <v>0.5122807017543859</v>
       </c>
       <c r="AJ2">
-        <v>0.3518518518518519</v>
+        <v>0.3349514563106796</v>
       </c>
       <c r="AK2">
-        <v>0.4462299134734239</v>
+        <v>0.4981949458483755</v>
       </c>
       <c r="AL2">
-        <v>0.556</v>
+        <v>0.908</v>
       </c>
       <c r="AM2">
-        <v>0.504</v>
+        <v>0.802</v>
       </c>
       <c r="AN2">
-        <v>-24.60122699386503</v>
+        <v>-81.1111111111111</v>
       </c>
       <c r="AO2">
-        <v>-6.205035971223022</v>
+        <v>-2.610132158590309</v>
       </c>
       <c r="AP2">
-        <v>-22.14723926380368</v>
+        <v>-76.66666666666666</v>
       </c>
       <c r="AQ2">
-        <v>-6.845238095238096</v>
+        <v>-2.955112219451371</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0906</v>
+        <v>-0.126</v>
       </c>
       <c r="G3">
-        <v>-0.02634146341463414</v>
+        <v>-0.0346264367816092</v>
       </c>
       <c r="H3">
-        <v>-0.02902439024390244</v>
+        <v>-0.03821839080459771</v>
       </c>
       <c r="I3">
-        <v>-0.08414634146341464</v>
+        <v>-0.06810344827586208</v>
       </c>
       <c r="J3">
-        <v>-0.08414634146341464</v>
+        <v>-0.06810344827586208</v>
       </c>
       <c r="K3">
-        <v>-3.27</v>
+        <v>-2.56</v>
       </c>
       <c r="L3">
-        <v>-0.07975609756097561</v>
+        <v>-0.07356321839080461</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="V3">
-        <v>0.06015037593984962</v>
+        <v>0.0291970802919708</v>
       </c>
       <c r="W3">
-        <v>-0.05978062157221206</v>
+        <v>-0.05714285714285715</v>
       </c>
       <c r="X3">
-        <v>0.1524809111683281</v>
+        <v>0.1196631312230006</v>
       </c>
       <c r="Y3">
-        <v>-0.2122615327405402</v>
+        <v>-0.1768059883658577</v>
       </c>
       <c r="Z3">
-        <v>0.4244745832901956</v>
+        <v>0.4301606922126081</v>
       </c>
       <c r="AA3">
-        <v>-0.03571798322807743</v>
+        <v>-0.02929542645241038</v>
       </c>
       <c r="AB3">
-        <v>0.1138804962909984</v>
+        <v>0.09402452015215366</v>
       </c>
       <c r="AC3">
-        <v>-0.1495984795190758</v>
+        <v>-0.1233199466045641</v>
       </c>
       <c r="AD3">
-        <v>40.1</v>
+        <v>43.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>40.1</v>
+        <v>43.8</v>
       </c>
       <c r="AG3">
-        <v>36.1</v>
+        <v>41.4</v>
       </c>
       <c r="AH3">
-        <v>0.376172607879925</v>
+        <v>0.3476190476190476</v>
       </c>
       <c r="AI3">
-        <v>0.4723203769140165</v>
+        <v>0.5122807017543859</v>
       </c>
       <c r="AJ3">
-        <v>0.3518518518518519</v>
+        <v>0.3349514563106796</v>
       </c>
       <c r="AK3">
-        <v>0.4462299134734239</v>
+        <v>0.4981949458483755</v>
       </c>
       <c r="AL3">
-        <v>0.556</v>
+        <v>0.908</v>
       </c>
       <c r="AM3">
-        <v>0.504</v>
+        <v>0.802</v>
       </c>
       <c r="AN3">
-        <v>-24.60122699386503</v>
+        <v>-81.1111111111111</v>
       </c>
       <c r="AO3">
-        <v>-6.205035971223022</v>
+        <v>-2.610132158590309</v>
       </c>
       <c r="AP3">
-        <v>-22.14723926380368</v>
+        <v>-76.66666666666666</v>
       </c>
       <c r="AQ3">
-        <v>-6.845238095238096</v>
+        <v>-2.955112219451371</v>
       </c>
     </row>
   </sheetData>
